--- a/output/pdf_financials_xlsx/LFE.xlsx
+++ b/output/pdf_financials_xlsx/LFE.xlsx
@@ -2312,37 +2312,37 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>7.607454</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>17.441514</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>32.981418</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>28.679603</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>12.316666</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>22.019661</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>34.806351</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>21.763365</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>18.152339</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>10.613986</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>20.410099</v>
       </c>
     </row>
     <row r="35">
@@ -2402,37 +2402,37 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>7.607454</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>17.441514</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>32.981418</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>28.679603</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>12.316666</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>22.019661</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>34.806351</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>21.763365</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>18.152339</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>10.613986</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>20.410099</v>
       </c>
     </row>
     <row r="37">
@@ -2948,31 +2948,31 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>195.363274</v>
+        <v>162.381856</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>248.842223</v>
+        <v>220.16262</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>240.704236</v>
+        <v>228.38757</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>248.738742</v>
+        <v>226.719081</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>237.519912</v>
+        <v>202.713561</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>201.211524</v>
+        <v>179.448159</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>209.960543</v>
+        <v>191.808204</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>173.350591</v>
+        <v>162.736605</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>169.432365</v>
+        <v>149.022266</v>
       </c>
     </row>
     <row r="49">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
